--- a/StructureDefinition-openimis-coverage-eligibility-response.xlsx
+++ b/StructureDefinition-openimis-coverage-eligibility-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9323,7 +9323,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>22</v>
@@ -9551,7 +9551,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>22</v>
@@ -9895,7 +9895,7 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>22</v>
@@ -10695,7 +10695,7 @@
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>22</v>
@@ -12063,7 +12063,7 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>22</v>
@@ -12179,7 +12179,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>22</v>
@@ -12639,7 +12639,7 @@
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>22</v>
@@ -12753,7 +12753,7 @@
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>22</v>
@@ -12867,7 +12867,7 @@
         <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>22</v>
@@ -13779,7 +13779,7 @@
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>22</v>
@@ -13893,7 +13893,7 @@
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>22</v>
@@ -14007,7 +14007,7 @@
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>22</v>
@@ -15951,7 +15951,7 @@
         <v>79</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>22</v>
@@ -16067,7 +16067,7 @@
         <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>22</v>
@@ -16183,7 +16183,7 @@
         <v>79</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>22</v>
@@ -16297,7 +16297,7 @@
         <v>79</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>22</v>
@@ -16643,7 +16643,7 @@
         <v>79</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>22</v>
@@ -16757,7 +16757,7 @@
         <v>79</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>22</v>
@@ -16871,7 +16871,7 @@
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>22</v>
@@ -17667,7 +17667,7 @@
         <v>79</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>22</v>
@@ -18465,7 +18465,7 @@
         <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>22</v>
@@ -19719,7 +19719,7 @@
         <v>79</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>22</v>
@@ -19833,7 +19833,7 @@
         <v>79</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>22</v>
@@ -19947,7 +19947,7 @@
         <v>79</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>22</v>
@@ -20061,7 +20061,7 @@
         <v>79</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>22</v>
@@ -20631,7 +20631,7 @@
         <v>79</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>22</v>
@@ -21089,7 +21089,7 @@
         <v>79</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>22</v>
@@ -21321,7 +21321,7 @@
         <v>79</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>22</v>
@@ -21437,7 +21437,7 @@
         <v>79</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>22</v>
@@ -21897,7 +21897,7 @@
         <v>79</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>22</v>
@@ -22011,7 +22011,7 @@
         <v>79</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>22</v>
@@ -22125,7 +22125,7 @@
         <v>79</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>22</v>
@@ -22921,7 +22921,7 @@
         <v>79</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>22</v>
@@ -23721,7 +23721,7 @@
         <v>79</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>22</v>
@@ -24521,7 +24521,7 @@
         <v>79</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>22</v>
@@ -24635,7 +24635,7 @@
         <v>79</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>22</v>
@@ -24749,7 +24749,7 @@
         <v>79</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>22</v>
@@ -24863,7 +24863,7 @@
         <v>79</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>22</v>
@@ -24977,7 +24977,7 @@
         <v>79</v>
       </c>
       <c r="G197" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H197" t="s" s="2">
         <v>22</v>
@@ -25091,7 +25091,7 @@
         <v>79</v>
       </c>
       <c r="G198" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H198" t="s" s="2">
         <v>22</v>
@@ -25207,7 +25207,7 @@
         <v>79</v>
       </c>
       <c r="G199" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H199" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-coverage-eligibility-response.xlsx
+++ b/StructureDefinition-openimis-coverage-eligibility-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-coverage-eligibility-response.xlsx
+++ b/StructureDefinition-openimis-coverage-eligibility-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
